--- a/ExtraSpell/package/LangMod/EN/Spells.xlsx
+++ b/ExtraSpell/package/LangMod/EN/Spells.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Elin\Package\Mod_ExtraSpell\LangMod\EN\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D3DE2A-805E-47A3-A691-47B5657A4359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-132" yWindow="1668" windowWidth="30852" windowHeight="14892" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12525"/>
   </bookViews>
   <sheets>
     <sheet name="Element" sheetId="1" r:id="rId1"/>
@@ -20,17 +14,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Element!$A$1:$BE$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="201">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +64,9 @@
     <t>parentFactor</t>
   </si>
   <si>
+    <t>lvFactor</t>
+  </si>
+  <si>
     <t>encFactor</t>
   </si>
   <si>
@@ -215,31 +220,61 @@
     <t>string[]</t>
   </si>
   <si>
+    <t>未设置</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>eleEther</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>ActArrow</t>
+  </si>
+  <si>
+    <t>SPELL</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>neg,repeat,domain</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>star_Fire</t>
+  </si>
+  <si>
     <t>火炎スターライト</t>
   </si>
   <si>
-    <t>MAG</t>
+    <t>Fire Star</t>
   </si>
   <si>
     <t>eleFire</t>
   </si>
   <si>
-    <t>Ground</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>SPELL</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>neg,repeat,domain</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>StarSpell</t>
+  </si>
+  <si>
+    <t>星光を放ち、小範囲にダメージを与えた後、十字型に広がり範囲内の対象に魔法ダメージを与える。</t>
+  </si>
+  <si>
+    <t>Emit starlight to deal damage in a small area, then tear into a cross-shaped burst, inflicting magical damage on targets within range.</t>
+  </si>
+  <si>
+    <t>範囲に#calcの#eleダメージを与える</t>
+  </si>
+  <si>
+    <t>Deal area #calc #ele damage.</t>
   </si>
   <si>
     <t>star_Cold</t>
@@ -248,6 +283,9 @@
     <t>冷気スターライト</t>
   </si>
   <si>
+    <t>Cold Star</t>
+  </si>
+  <si>
     <t>eleCold</t>
   </si>
   <si>
@@ -257,6 +295,9 @@
     <t>電撃スターライト</t>
   </si>
   <si>
+    <t>Lightning Star</t>
+  </si>
+  <si>
     <t>eleLightning</t>
   </si>
   <si>
@@ -266,6 +307,9 @@
     <t>暗黒スターライト</t>
   </si>
   <si>
+    <t>Darkness Star</t>
+  </si>
+  <si>
     <t>eleDarkness</t>
   </si>
   <si>
@@ -275,6 +319,9 @@
     <t>幻惑スターライト</t>
   </si>
   <si>
+    <t>Mind Star</t>
+  </si>
+  <si>
     <t>CHA</t>
   </si>
   <si>
@@ -287,6 +334,9 @@
     <t>毒スターライト</t>
   </si>
   <si>
+    <t>Poison Star</t>
+  </si>
+  <si>
     <t>DEX</t>
   </si>
   <si>
@@ -299,6 +349,9 @@
     <t>地獄スターライト</t>
   </si>
   <si>
+    <t>Nether Star</t>
+  </si>
+  <si>
     <t>END</t>
   </si>
   <si>
@@ -311,6 +364,9 @@
     <t>轟音スターライト</t>
   </si>
   <si>
+    <t>Sound Star</t>
+  </si>
+  <si>
     <t>PER</t>
   </si>
   <si>
@@ -323,6 +379,9 @@
     <t>神経スターライト</t>
   </si>
   <si>
+    <t>Nerve Star</t>
+  </si>
+  <si>
     <t>LER</t>
   </si>
   <si>
@@ -335,6 +394,9 @@
     <t>神聖スターライト</t>
   </si>
   <si>
+    <t>Holy Star</t>
+  </si>
+  <si>
     <t>WIL</t>
   </si>
   <si>
@@ -347,6 +409,9 @@
     <t>混沌スターライト</t>
   </si>
   <si>
+    <t>Chaos Star</t>
+  </si>
+  <si>
     <t>eleChaos</t>
   </si>
   <si>
@@ -356,6 +421,9 @@
     <t>魔法スターライト</t>
   </si>
   <si>
+    <t>Magic Star</t>
+  </si>
+  <si>
     <t>eleMagic</t>
   </si>
   <si>
@@ -365,7 +433,7 @@
     <t>エーテルスターライト</t>
   </si>
   <si>
-    <t>eleEther</t>
+    <t>Ether Star</t>
   </si>
   <si>
     <t>star_Acid</t>
@@ -374,6 +442,9 @@
     <t>酸スターライト</t>
   </si>
   <si>
+    <t>Acid Star</t>
+  </si>
+  <si>
     <t>eleAcid</t>
   </si>
   <si>
@@ -383,6 +454,9 @@
     <t>出血スターライト</t>
   </si>
   <si>
+    <t>Cut Star</t>
+  </si>
+  <si>
     <t>STR</t>
   </si>
   <si>
@@ -395,52 +469,69 @@
     <t>衝撃スターライト</t>
   </si>
   <si>
+    <t>Impact Star</t>
+  </si>
+  <si>
     <t>eleImpact</t>
   </si>
   <si>
-    <t>lvFactor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未设置</t>
-  </si>
-  <si>
-    <t>ActArrow</t>
-  </si>
-  <si>
-    <t>star_Fire</t>
-  </si>
-  <si>
-    <t>StarSpell</t>
-  </si>
-  <si>
-    <t>星光を放ち、小範囲にダメージを与えた後、十字型に広がり範囲内の対象に魔法ダメージを与える。</t>
-  </si>
-  <si>
     <t>chain_Lightning</t>
   </si>
   <si>
     <t>連鎖稲妻</t>
   </si>
   <si>
+    <t>Chain Lightning</t>
+  </si>
+  <si>
     <t>LightningSpell</t>
   </si>
   <si>
     <t>対象に稲妻を放ち、敵の間を連鎖して隣接する敵に複数回の魔法ダメージを与える。</t>
   </si>
   <si>
+    <t>Release a bolt of lightning at the target that jumps between enemies, dealing multiple instances of magical damage to nearby foes.</t>
+  </si>
+  <si>
     <t>blowback</t>
   </si>
   <si>
     <t>吹き飛ばし</t>
   </si>
   <si>
+    <t>Blowback</t>
+  </si>
+  <si>
     <t>BlowbackSpell</t>
   </si>
   <si>
     <t>魔力の強風を放ち、範囲内の対象を吹き飛ばしてわずかなダメージを与える。</t>
   </si>
   <si>
+    <t>Unleash a magical gust of wind that knocks back targets within range, dealing minor damage.</t>
+  </si>
+  <si>
+    <t>範囲に#calcの#eleダメージを与え、敵を吹き飛ばす</t>
+  </si>
+  <si>
+    <t>Deal area #calc #ele damage and knock back enemies.</t>
+  </si>
+  <si>
+    <t>Gather</t>
+  </si>
+  <si>
+    <t>集まる</t>
+  </si>
+  <si>
+    <t>GatherSpell</t>
+  </si>
+  <si>
+    <t>周囲の敵を一点に集める。</t>
+  </si>
+  <si>
+    <t>Gather the surrounding enemies to a single point.</t>
+  </si>
+  <si>
     <t>black_Hole</t>
   </si>
   <si>
@@ -450,88 +541,6 @@
     <t>BHoleSpell</t>
   </si>
   <si>
-    <t>Fire Star</t>
-  </si>
-  <si>
-    <t>Cold Star</t>
-  </si>
-  <si>
-    <t>Lightning Star</t>
-  </si>
-  <si>
-    <t>Darkness Star</t>
-  </si>
-  <si>
-    <t>Mind Star</t>
-  </si>
-  <si>
-    <t>Poison Star</t>
-  </si>
-  <si>
-    <t>Nether Star</t>
-  </si>
-  <si>
-    <t>Sound Star</t>
-  </si>
-  <si>
-    <t>Nerve Star</t>
-  </si>
-  <si>
-    <t>Holy Star</t>
-  </si>
-  <si>
-    <t>Chaos Star</t>
-  </si>
-  <si>
-    <t>Magic Star</t>
-  </si>
-  <si>
-    <t>Ether Star</t>
-  </si>
-  <si>
-    <t>Acid Star</t>
-  </si>
-  <si>
-    <t>Cut Star</t>
-  </si>
-  <si>
-    <t>Impact Star</t>
-  </si>
-  <si>
-    <t>Chain Lightning</t>
-  </si>
-  <si>
-    <t>Blowback</t>
-  </si>
-  <si>
-    <t>Unleash a magical gust of wind that knocks back targets within range, dealing minor damage.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Release a bolt of lightning at the target that jumps between enemies, dealing multiple instances of magical damage to nearby foes.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Emit starlight to deal damage in a small area, then tear into a cross-shaped burst, inflicting magical damage on targets within range.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deal area #calc #ele damage and knock back enemies.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deal area #calc #ele damage.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>範囲に#calcの#eleダメージを与え、敵を吹き飛ばす</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>範囲に#calcの#eleダメージを与える</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>num</t>
   </si>
   <si>
@@ -577,81 +586,109 @@
     <t>ES_Fix_Nus</t>
   </si>
   <si>
+    <t>[ExtraSpell] Error: &lt;alias&gt;{0}はありません</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ExtraSpell] Error: Could not find magic with alias {0} </t>
+  </si>
+  <si>
     <t>ES_Shop_Nus</t>
-  </si>
-  <si>
-    <t>ES_Shop_FormatError</t>
-  </si>
-  <si>
-    <t>[ExtraSpell] Error: 商人:{0} フォーマットは間違いです</t>
-  </si>
-  <si>
-    <t>ES_Shop_BagSpawnError</t>
-  </si>
-  <si>
-    <t>[ExtraSpell] Error: 商人:商人の鞄を形成することができません: {0}</t>
-  </si>
-  <si>
-    <t>ES_Fix_Done</t>
-  </si>
-  <si>
-    <t>ES_Fix_AllDone</t>
-  </si>
-  <si>
-    <t>[ExtraSpell] Info: 魔法は全部更新しました</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ExtraSpell] Error: Merchant: Incorrect format for {0}  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ExtraSpell] Error: Merchant: Unable to generate merchant space: {0}  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ExtraSpell] Info: All spells have been updated  </t>
-  </si>
-  <si>
-    <t>[ExtraSpell] Info: 魔法を更新した - Alias: {0}, Radius: {1}, Cost: {2}, Value: {3}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[ExtraSpell] Info: Updating magic - Alias: {0}, Radius: {1}, Cost: {2}, Value: {3}  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[ExtraSpell] Error: &lt;alias&gt;{0}はありません</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[ExtraSpell] Error: 商人:&lt;alias&gt;{0}はありません
 一回生成をスキップしました</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[ExtraSpell] Error: Could not find magic with alias {0} </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[ExtraSpell] Error: Merchant: No corresponding magic in spell list {0} 
 skipped once create</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES_Shop_FormatError</t>
+  </si>
+  <si>
+    <t>[ExtraSpell] Error: 商人:{0} フォーマットは間違いです</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ExtraSpell] Error: Merchant: Incorrect format for {0}  </t>
+  </si>
+  <si>
+    <t>ES_Shop_BagSpawnError</t>
+  </si>
+  <si>
+    <t>[ExtraSpell] Error: 商人:商人の鞄を形成することができません: {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ExtraSpell] Error: Merchant: Unable to generate merchant space: {0}  </t>
+  </si>
+  <si>
+    <t>ES_Fix_Done</t>
+  </si>
+  <si>
+    <t>[ExtraSpell] Info: 魔法を更新した - Alias: {0}, Radius: {1}, Cost: {2}, Value: {3}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ExtraSpell] Info: Updating magic - Alias: {0}, Radius: {1}, Cost: {2}, Value: {3}  </t>
+  </si>
+  <si>
+    <t>ES_Fix_AllDone</t>
+  </si>
+  <si>
+    <t>[ExtraSpell] Info: 魔法は全部更新しました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ExtraSpell] Info: All spells have been updated  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -659,50 +696,170 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -711,12 +868,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -724,36 +1067,326 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常規" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="貨幣" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="貨幣[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超鏈接" xfId="6" builtinId="8"/>
+    <cellStyle name="已訪問的超鏈接" xfId="7" builtinId="9"/>
+    <cellStyle name="註釋" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文字" xfId="9" builtinId="11"/>
+    <cellStyle name="標題" xfId="10" builtinId="15"/>
+    <cellStyle name="解釋性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="標題 1" xfId="12" builtinId="16"/>
+    <cellStyle name="標題 2" xfId="13" builtinId="17"/>
+    <cellStyle name="標題 3" xfId="14" builtinId="18"/>
+    <cellStyle name="標題 4" xfId="15" builtinId="19"/>
+    <cellStyle name="輸入" xfId="16" builtinId="20"/>
+    <cellStyle name="輸出" xfId="17" builtinId="21"/>
+    <cellStyle name="計算" xfId="18" builtinId="22"/>
+    <cellStyle name="檢查儲存格" xfId="19" builtinId="23"/>
+    <cellStyle name="鏈接儲存格" xfId="20" builtinId="24"/>
+    <cellStyle name="匯總" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="適中" xfId="24" builtinId="28"/>
+    <cellStyle name="強調文字顏色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 強調文字顏色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 強調文字顏色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 強調文字顏色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="強調文字顏色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 強調文字顏色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 強調文字顏色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 強調文字顏色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="強調文字顏色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 強調文字顏色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 強調文字顏色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 強調文字顏色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="強調文字顏色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 強調文字顏色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 強調文字顏色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 強調文字顏色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="強調文字顏色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 強調文字顏色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 強調文字顏色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 強調文字顏色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="強調文字顏色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 強調文字顏色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 強調文字顏色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 強調文字顏色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -802,7 +1435,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -837,7 +1470,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -1011,467 +1644,462 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:BE25"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:57">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AC1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AD1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AF1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AH1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AI1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AK1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AL1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AM1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AN1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AP1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AR1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AS1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AT1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AU1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AV1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AW1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AX1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AY1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BA1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BB1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BC1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BD1" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="BE1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="2" s="7" customFormat="1" spans="1:57">
+      <c r="A2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="L2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="M2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="O2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="P2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="Q2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="R2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="S2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="T2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="U2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="AH2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="W2" s="1" t="s">
+      <c r="AI2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="AL2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AT2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AV2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AW2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AX2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AY2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AZ2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="BB2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BD2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE2" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" s="7" customFormat="1" spans="4:49">
+      <c r="D3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="G3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="7">
         <v>5</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="7">
         <v>100</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="7">
         <v>100</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="7">
         <v>1</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="7">
         <v>1</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="7">
         <v>100</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="7">
         <v>300</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="7">
         <v>10</v>
       </c>
-      <c r="T3" s="1">
+      <c r="T3" s="7">
         <v>0</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V3" s="1" t="s">
+      <c r="U3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="X3" s="1" t="s">
+      <c r="V3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="W3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="AA3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB3" s="1" t="s">
+      <c r="X3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="Z3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="AD3" s="1">
+      <c r="AA3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD3" s="7">
         <v>50</v>
       </c>
-      <c r="AE3" s="1">
+      <c r="AE3" s="7">
         <v>0</v>
       </c>
-      <c r="AF3" s="1">
+      <c r="AF3" s="7">
         <v>16</v>
       </c>
-      <c r="AG3" s="1">
+      <c r="AG3" s="7">
         <v>0</v>
       </c>
-      <c r="AH3" s="1">
+      <c r="AH3" s="7">
         <v>0</v>
       </c>
-      <c r="AK3" s="1">
+      <c r="AK3" s="7">
         <v>0</v>
       </c>
-      <c r="AS3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="AS3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW3" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49">
       <c r="A4">
         <v>53800</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -1483,7 +2111,7 @@
         <v>8</v>
       </c>
       <c r="W4" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD4">
         <v>60</v>
@@ -1495,36 +2123,36 @@
         <v>3.5</v>
       </c>
       <c r="AR4" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS4" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV4" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49">
       <c r="A5">
         <v>53801</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1536,7 +2164,7 @@
         <v>8</v>
       </c>
       <c r="W5" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD5">
         <v>60</v>
@@ -1548,36 +2176,36 @@
         <v>3.5</v>
       </c>
       <c r="AR5" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS5" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV5" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49">
       <c r="A6">
         <v>53802</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -1589,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="W6" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD6">
         <v>60</v>
@@ -1601,36 +2229,36 @@
         <v>3.5</v>
       </c>
       <c r="AR6" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS6" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV6" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49">
       <c r="A7">
         <v>53803</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1642,7 +2270,7 @@
         <v>8</v>
       </c>
       <c r="W7" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD7">
         <v>60</v>
@@ -1654,36 +2282,36 @@
         <v>3.5</v>
       </c>
       <c r="AR7" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS7" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV7" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49">
       <c r="A8">
         <v>53804</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -1695,7 +2323,7 @@
         <v>8</v>
       </c>
       <c r="W8" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD8">
         <v>60</v>
@@ -1707,36 +2335,36 @@
         <v>3.5</v>
       </c>
       <c r="AR8" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS8" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV8" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49">
       <c r="A9">
         <v>53805</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -1748,7 +2376,7 @@
         <v>8</v>
       </c>
       <c r="W9" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD9">
         <v>60</v>
@@ -1760,36 +2388,36 @@
         <v>3.5</v>
       </c>
       <c r="AR9" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS9" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV9" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49">
       <c r="A10">
         <v>53806</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -1801,7 +2429,7 @@
         <v>8</v>
       </c>
       <c r="W10" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD10">
         <v>60</v>
@@ -1813,36 +2441,36 @@
         <v>3.5</v>
       </c>
       <c r="AR10" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS10" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV10" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49">
       <c r="A11">
         <v>53807</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="O11">
         <v>5</v>
@@ -1854,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="W11" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD11">
         <v>60</v>
@@ -1866,36 +2494,36 @@
         <v>3.5</v>
       </c>
       <c r="AR11" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS11" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV11" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49">
       <c r="A12">
         <v>53808</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -1907,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="W12" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD12">
         <v>60</v>
@@ -1919,36 +2547,36 @@
         <v>3.5</v>
       </c>
       <c r="AR12" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS12" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV12" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:49">
       <c r="A13">
         <v>53809</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="H13" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -1960,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="W13" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD13">
         <v>60</v>
@@ -1972,36 +2600,36 @@
         <v>3.5</v>
       </c>
       <c r="AR13" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS13" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV13" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:49">
       <c r="A14">
         <v>53810</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -2013,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="W14" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD14">
         <v>60</v>
@@ -2025,36 +2653,36 @@
         <v>3.5</v>
       </c>
       <c r="AR14" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS14" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV14" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:49">
       <c r="A15">
         <v>53811</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -2066,7 +2694,7 @@
         <v>8</v>
       </c>
       <c r="W15" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD15">
         <v>60</v>
@@ -2078,36 +2706,36 @@
         <v>3.5</v>
       </c>
       <c r="AR15" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS15" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV15" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:49">
       <c r="A16">
         <v>53812</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -2119,7 +2747,7 @@
         <v>8</v>
       </c>
       <c r="W16" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD16">
         <v>60</v>
@@ -2131,36 +2759,36 @@
         <v>3.5</v>
       </c>
       <c r="AR16" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS16" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV16" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49">
       <c r="A17">
         <v>53813</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2172,7 +2800,7 @@
         <v>8</v>
       </c>
       <c r="W17" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD17">
         <v>60</v>
@@ -2184,36 +2812,36 @@
         <v>3.5</v>
       </c>
       <c r="AR17" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS17" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV17" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW17" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49">
       <c r="A18">
         <v>53814</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -2225,7 +2853,7 @@
         <v>8</v>
       </c>
       <c r="W18" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD18">
         <v>60</v>
@@ -2237,36 +2865,36 @@
         <v>3.5</v>
       </c>
       <c r="AR18" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS18" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV18" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW18" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49">
       <c r="A19">
         <v>53815</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -2278,7 +2906,7 @@
         <v>8</v>
       </c>
       <c r="W19" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="AD19">
         <v>60</v>
@@ -2290,36 +2918,36 @@
         <v>3.5</v>
       </c>
       <c r="AR19" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="AS19" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AV19" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW19" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49">
       <c r="A20">
         <v>333001</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2334,7 +2962,7 @@
         <v>13</v>
       </c>
       <c r="W20" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AF20">
         <v>10</v>
@@ -2343,36 +2971,36 @@
         <v>2</v>
       </c>
       <c r="AR20" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="AS20" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="AV20" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AW20" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49">
       <c r="A21">
         <v>333002</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H21" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="P21">
         <v>300</v>
@@ -2384,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="W21" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="AD21">
         <v>1</v>
@@ -2396,30 +3024,78 @@
         <v>4</v>
       </c>
       <c r="AR21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS21" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="AS21" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="AV21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AW21" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="22" s="8" customFormat="1" spans="1:45">
+      <c r="A22" s="8">
+        <v>333003</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="P22" s="9">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>200</v>
+      </c>
+      <c r="R22" s="9">
+        <v>1</v>
+      </c>
+      <c r="U22" s="9"/>
+      <c r="W22" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD22" s="8">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="8">
+        <v>20</v>
+      </c>
+      <c r="AG22" s="8">
+        <v>4</v>
+      </c>
+      <c r="AR22" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS22" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="2:33">
       <c r="B25" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="P25">
         <v>300</v>
@@ -2431,7 +3107,7 @@
         <v>50</v>
       </c>
       <c r="W25" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="AF25">
         <v>3</v>
@@ -2441,49 +3117,50 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3E31A2-8057-4B3E-B808-BB66887509BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="3:4">
       <c r="C3">
         <v>233</v>
       </c>
@@ -2491,178 +3168,179 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" t="s">
-        <v>168</v>
-      </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1438E2FD-16B5-404B-AA7E-F8FB2D1D4915}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
-    <col min="3" max="4" width="73.44140625" customWidth="1"/>
+    <col min="1" max="1" width="23.4380952380952" customWidth="1"/>
+    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
+    <col min="3" max="4" width="73.4380952380952" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="8" t="s">
+      <c r="B1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="8" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="4" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>189</v>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>